--- a/data/trans_camb/P16A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -1,93</t>
+          <t>-7,27; -1,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -2,08</t>
+          <t>-7,52; -2,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; -0,94</t>
+          <t>-6,28; -0,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,49</t>
+          <t>-2,1; 5,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,3</t>
+          <t>-4,84; 1,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,87</t>
+          <t>-2,98; 2,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,09</t>
+          <t>-4,08; 0,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -1,55</t>
+          <t>-5,62; -1,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,02</t>
+          <t>-4,11; -0,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,61; -36,38</t>
+          <t>-93,24; -39,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-93,43; -39,47</t>
+          <t>-93,95; -45,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,91; -19,64</t>
+          <t>-81,56; -19,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 157,48</t>
+          <t>-36,09; 189,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 49,79</t>
+          <t>-72,63; 61,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 98,33</t>
+          <t>-43,53; 97,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 3,48</t>
+          <t>-62,57; 7,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,77; -29,09</t>
+          <t>-80,16; -26,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 4,79</t>
+          <t>-58,97; -1,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,88</t>
+          <t>-1,19; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,22</t>
+          <t>-1,11; 2,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,81</t>
+          <t>-1,16; 1,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 8,17</t>
+          <t>0,55; 8,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,94</t>
+          <t>-2,05; 4,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,88</t>
+          <t>-3,06; 1,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,19</t>
+          <t>-0,01; 4,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,42</t>
+          <t>-1,05; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,28</t>
+          <t>-1,57; 1,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 929,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,09; 785,45</t>
+          <t>-80,31; 705,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,66; 748,72</t>
+          <t>-72,96; 650,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 344,84</t>
+          <t>4,24; 330,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 187,04</t>
+          <t>-43,21; 168,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 93,11</t>
+          <t>-55,99; 82,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 291,35</t>
+          <t>-4,35; 255,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 157,06</t>
+          <t>-36,51; 169,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 95,82</t>
+          <t>-49,26; 82,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,0</t>
+          <t>-2,39; 1,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,07</t>
+          <t>-3,3; -0,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,05</t>
+          <t>-3,27; 1,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,86</t>
+          <t>-9,0; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 3,53</t>
+          <t>-7,61; 3,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,94</t>
+          <t>-4,36; 6,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,56</t>
+          <t>-3,11; 0,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,03</t>
+          <t>-3,47; -0,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,92</t>
+          <t>-3,69; 1,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 64,1</t>
+          <t>-74,47; 70,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,41; 17,38</t>
+          <t>-91,42; 6,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,09; 53,09</t>
+          <t>-82,52; 65,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 26,06</t>
+          <t>-79,09; 24,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 76,75</t>
+          <t>-72,79; 80,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 143,57</t>
+          <t>-40,72; 138,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 21,42</t>
+          <t>-65,43; 23,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,84; 4,21</t>
+          <t>-74,07; 0,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 59,2</t>
+          <t>-72,13; 52,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,41</t>
+          <t>-1,52; 0,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,19</t>
+          <t>-0,92; 1,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,97</t>
+          <t>-0,26; 1,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,03</t>
+          <t>-0,71; 3,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,73</t>
+          <t>-2,33; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,1</t>
+          <t>-3,53; 1,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,43</t>
+          <t>-0,77; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,04</t>
+          <t>-1,13; 0,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,39</t>
+          <t>-0,86; 1,39</t>
         </is>
       </c>
     </row>
@@ -1431,42 +1431,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 44,77</t>
+          <t>-69,54; 51,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 105,3</t>
+          <t>-45,18; 121,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 188,92</t>
+          <t>-14,73; 183,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 114,63</t>
+          <t>-13,75; 114,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 53,43</t>
+          <t>-42,99; 56,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 28,69</t>
+          <t>-65,65; 34,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 66,14</t>
+          <t>-23,59; 66,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 48,77</t>
+          <t>-35,76; 40,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,71</t>
+          <t>-3,35; 0,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,46</t>
+          <t>-3,38; 0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,48</t>
+          <t>-1,81; 2,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,66</t>
+          <t>0,93; 5,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,57</t>
+          <t>-1,9; 2,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,71</t>
+          <t>-0,55; 3,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,1</t>
+          <t>-0,17; 3,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,98</t>
+          <t>-1,97; 0,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,8</t>
+          <t>-0,33; 2,79</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 81,97</t>
+          <t>-84,6; 73,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,91; 52,69</t>
+          <t>-81,86; 48,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 252,29</t>
+          <t>-53,63; 210,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,53; 234,45</t>
+          <t>14,89; 230,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 110,97</t>
+          <t>-40,67; 106,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 143,46</t>
+          <t>-13,18; 151,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 135,27</t>
+          <t>-6,92; 138,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 43,04</t>
+          <t>-47,27; 45,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 122,13</t>
+          <t>-7,65; 121,04</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,63</t>
+          <t>-0,31; 2,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,98</t>
+          <t>-0,63; 0,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,0</t>
+          <t>-0,63; 3,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,11</t>
+          <t>-3,69; -0,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,46; -0,47</t>
+          <t>-4,34; -0,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,65</t>
+          <t>-3,44; 0,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,37</t>
+          <t>-2,96; 0,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,49</t>
+          <t>-3,71; -0,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,39</t>
+          <t>-2,93; 0,34</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 3,06</t>
+          <t>-47,77; 1,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,18; -7,32</t>
+          <t>-55,46; -10,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 12,04</t>
+          <t>-42,53; 9,75</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 8,87</t>
+          <t>-45,39; 6,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-57,28; -10,18</t>
+          <t>-56,3; -9,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 8,49</t>
+          <t>-43,89; 8,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; -0,17</t>
+          <t>-1,57; -0,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; -0,22</t>
+          <t>-1,61; -0,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,53</t>
+          <t>-0,97; 0,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,8</t>
+          <t>-0,43; 1,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,06</t>
+          <t>-2,26; -0,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,58</t>
+          <t>-1,59; 0,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,56</t>
+          <t>-0,8; 0,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; -0,43</t>
+          <t>-1,69; -0,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,34</t>
+          <t>-1,04; 0,39</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-60,2; -9,35</t>
+          <t>-61,74; -10,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,0; -12,06</t>
+          <t>-60,93; -14,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 28,03</t>
+          <t>-36,81; 30,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 37,66</t>
+          <t>-7,6; 37,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,08; -1,65</t>
+          <t>-37,91; -1,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 12,77</t>
+          <t>-27,56; 12,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 16,45</t>
+          <t>-19,52; 16,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-41,51; -12,27</t>
+          <t>-40,78; -12,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 9,54</t>
+          <t>-26,41; 10,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -1,87</t>
+          <t>-7,41; -2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -2,35</t>
+          <t>-7,47; -2,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,97</t>
+          <t>-6,52; -1,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,74</t>
+          <t>-1,9; 5,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,58</t>
+          <t>-4,99; 1,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,9</t>
+          <t>-3,35; 2,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,26</t>
+          <t>-4,11; 0,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -1,45</t>
+          <t>-5,33; -1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,15</t>
+          <t>-4,03; -0,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-60,15%</t>
+          <t>-62,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-34,74%</t>
+          <t>-36,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-93,24; -39,46</t>
+          <t>-93,62; -44,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-93,95; -45,77</t>
+          <t>-93,02; -47,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,56; -19,33</t>
+          <t>-83,95; -21,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 189,46</t>
+          <t>-36,29; 169,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 61,55</t>
+          <t>-72,42; 64,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 97,12</t>
+          <t>-48,33; 84,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 7,11</t>
+          <t>-62,52; 8,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,16; -26,74</t>
+          <t>-80,16; -30,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,97; -1,87</t>
+          <t>-58,85; -3,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,52</t>
+          <t>-1,09; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,33</t>
+          <t>-1,2; 2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,89</t>
+          <t>-1,2; 1,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,26</t>
+          <t>0,41; 7,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,06</t>
+          <t>-2,23; 4,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,83</t>
+          <t>-2,95; 1,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,17</t>
+          <t>0,02; 4,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,4</t>
+          <t>-1,02; 2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,24</t>
+          <t>-1,48; 1,38</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-8,32%</t>
+          <t>-11,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-1,88%</t>
+          <t>-2,37%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 929,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,31; 705,89</t>
+          <t>-82,56; 837,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 650,73</t>
+          <t>-71,53; 680,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 330,09</t>
+          <t>2,31; 286,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 168,73</t>
+          <t>-45,93; 173,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 82,38</t>
+          <t>-56,55; 80,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 255,14</t>
+          <t>-5,92; 246,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 169,11</t>
+          <t>-33,53; 158,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 82,44</t>
+          <t>-45,62; 101,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,15</t>
+          <t>-2,58; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,15</t>
+          <t>-3,36; -0,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,22</t>
+          <t>-1,58; 2,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 0,88</t>
+          <t>-8,48; 1,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 3,43</t>
+          <t>-7,53; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 6,54</t>
+          <t>-4,31; 7,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,57</t>
+          <t>-2,99; 0,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,03</t>
+          <t>-3,5; 0,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,77</t>
+          <t>-1,2; 3,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-28,48%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,42%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 70,18</t>
+          <t>-74,09; 72,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,42; 6,91</t>
+          <t>-88,2; 12,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,52; 65,64</t>
+          <t>-49,2; 139,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 24,56</t>
+          <t>-76,89; 37,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 80,57</t>
+          <t>-72,25; 86,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 138,12</t>
+          <t>-37,84; 158,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 23,56</t>
+          <t>-64,98; 26,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 0,99</t>
+          <t>-71,49; 8,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 52,27</t>
+          <t>-26,72; 111,49</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,35</t>
+          <t>-1,43; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,2</t>
+          <t>-0,96; 1,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,89</t>
+          <t>-0,06; 2,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,97</t>
+          <t>-0,87; 4,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,88</t>
+          <t>-2,62; 1,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,26</t>
+          <t>-1,27; 2,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,41</t>
+          <t>-0,72; 1,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,94</t>
+          <t>-1,07; 1,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,39</t>
+          <t>-0,07; 2,02</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,08%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 51,32</t>
+          <t>-71,18; 39,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 121,31</t>
+          <t>-48,59; 111,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 183,35</t>
+          <t>-8,39; 220,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 114,47</t>
+          <t>-16,56; 113,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 56,29</t>
+          <t>-47,71; 52,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,65; 34,18</t>
+          <t>-23,61; 79,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 66,05</t>
+          <t>-23,05; 69,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 40,37</t>
+          <t>-33,37; 45,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 65,46</t>
+          <t>-2,61; 96,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,7</t>
+          <t>-3,21; 0,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,41</t>
+          <t>-3,37; 0,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,5</t>
+          <t>-2,28; 1,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,81</t>
+          <t>0,83; 6,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,65</t>
+          <t>-2,03; 2,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,65</t>
+          <t>0,34; 4,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,18</t>
+          <t>-0,05; 3,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,99</t>
+          <t>-2,1; 0,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,79</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-84,6; 73,85</t>
+          <t>-83,57; 62,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 48,59</t>
+          <t>-84,74; 43,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,63; 210,64</t>
+          <t>-60,54; 151,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,89; 230,55</t>
+          <t>14,03; 244,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 106,61</t>
+          <t>-41,24; 92,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 151,29</t>
+          <t>4,27; 165,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 138,55</t>
+          <t>-4,7; 129,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 45,75</t>
+          <t>-49,18; 37,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 121,04</t>
+          <t>-0,71; 135,75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,54</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,54</t>
+          <t>-0,28; 2,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,99</t>
+          <t>-0,63; 1,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,61</t>
+          <t>-0,63; 2,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,02</t>
+          <t>-3,71; 0,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -0,61</t>
+          <t>-4,38; -0,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,57</t>
+          <t>-3,7; 0,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,27</t>
+          <t>-2,96; 0,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,71; -0,47</t>
+          <t>-3,68; -0,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,34</t>
+          <t>-3,1; 0,16</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>138,46%</t>
+          <t>121,62%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-19,55%</t>
+          <t>-26,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-21,9%</t>
+          <t>-27,38%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 1,27</t>
+          <t>-47,1; 4,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -10,57</t>
+          <t>-55,73; -8,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-42,53; 9,75</t>
+          <t>-46,39; 5,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 6,77</t>
+          <t>-46,65; 7,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,3; -9,5</t>
+          <t>-57,43; -13,24</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 8,46</t>
+          <t>-48,0; 3,44</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,2</t>
+          <t>-1,56; -0,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,29</t>
+          <t>-1,6; -0,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,58</t>
+          <t>-0,78; 0,7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,8</t>
+          <t>-0,52; 1,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,11</t>
+          <t>-2,13; -0,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,63</t>
+          <t>-1,02; 0,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,56</t>
+          <t>-0,86; 0,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,44</t>
+          <t>-1,67; -0,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,39</t>
+          <t>-0,63; 0,62</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-8,94%</t>
+          <t>-0,11%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-8,18%</t>
+          <t>-1,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-7,95%</t>
+          <t>-0,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-61,74; -10,16</t>
+          <t>-61,15; -11,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,93; -14,47</t>
+          <t>-61,28; -12,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 30,33</t>
+          <t>-29,1; 36,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 37,08</t>
+          <t>-8,67; 38,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,91; -1,89</t>
+          <t>-36,12; -1,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 12,08</t>
+          <t>-17,27; 21,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 16,34</t>
+          <t>-20,18; 16,18</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -12,95</t>
+          <t>-40,1; -12,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 10,97</t>
+          <t>-15,12; 18,18</t>
         </is>
       </c>
     </row>
